--- a/docs/3조_1차 프로젝트_WBS.v2.xlsx
+++ b/docs/3조_1차 프로젝트_WBS.v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\spring_workspace\recycle\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3F28C9-DE06-4537-A7E7-15A09D68FACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAE612C-5754-45C7-8D4C-29F204BC4ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1699,13 +1699,133 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1722,126 +1842,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2185,10 +2185,10 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="134" t="s">
+      <c r="C2" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="134"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="24"/>
       <c r="H2" s="3"/>
     </row>
@@ -2196,10 +2196,10 @@
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="135" t="s">
+      <c r="C3" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="136"/>
+      <c r="D3" s="112"/>
       <c r="E3" s="25"/>
       <c r="H3" s="3"/>
     </row>
@@ -2207,10 +2207,10 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="117" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="136"/>
+      <c r="D4" s="112"/>
       <c r="E4" s="25"/>
       <c r="H4" s="3"/>
     </row>
@@ -2218,10 +2218,10 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="136" t="s">
+      <c r="C5" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="136"/>
+      <c r="D5" s="112"/>
       <c r="E5" s="25"/>
       <c r="H5" s="3"/>
     </row>
@@ -2229,10 +2229,10 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="136" t="s">
+      <c r="C6" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="136"/>
+      <c r="D6" s="112"/>
       <c r="E6" s="25"/>
       <c r="H6" s="3"/>
     </row>
@@ -2240,10 +2240,10 @@
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="136" t="s">
+      <c r="C7" s="112" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="136"/>
+      <c r="D7" s="112"/>
       <c r="E7" s="25"/>
       <c r="H7" s="3"/>
     </row>
@@ -2296,46 +2296,46 @@
       </c>
     </row>
     <row r="10" spans="2:51" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="109" t="s">
+      <c r="B10" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="111" t="s">
+      <c r="C10" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="114" t="s">
+      <c r="D10" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="114" t="s">
+      <c r="E10" s="110" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="114" t="s">
+      <c r="F10" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="114" t="s">
+      <c r="G10" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="114" t="s">
+      <c r="H10" s="110" t="s">
         <v>10</v>
       </c>
       <c r="I10" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="146" t="s">
+      <c r="J10" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
-      <c r="M10" s="147"/>
-      <c r="N10" s="147"/>
-      <c r="O10" s="147"/>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="147"/>
-      <c r="R10" s="147"/>
-      <c r="S10" s="147"/>
-      <c r="T10" s="147"/>
-      <c r="U10" s="147"/>
-      <c r="V10" s="147"/>
-      <c r="W10" s="148"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="114"/>
+      <c r="Q10" s="114"/>
+      <c r="R10" s="114"/>
+      <c r="S10" s="114"/>
+      <c r="T10" s="114"/>
+      <c r="U10" s="114"/>
+      <c r="V10" s="114"/>
+      <c r="W10" s="115"/>
       <c r="X10" s="8"/>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -2364,33 +2364,33 @@
       <c r="AW10" s="8"/>
     </row>
     <row r="11" spans="2:51" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="110"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
       <c r="I11" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="140" t="s">
+      <c r="J11" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="142"/>
-      <c r="P11" s="143" t="s">
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="144"/>
-      <c r="U11" s="144"/>
-      <c r="V11" s="145"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="108"/>
+      <c r="S11" s="108"/>
+      <c r="T11" s="108"/>
+      <c r="U11" s="108"/>
+      <c r="V11" s="109"/>
       <c r="W11" s="100" t="s">
         <v>141</v>
       </c>
@@ -2418,13 +2418,13 @@
       <c r="AY11" s="5"/>
     </row>
     <row r="12" spans="2:51" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="110"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
       <c r="I12" s="31" t="s">
         <v>14</v>
       </c>
@@ -2498,10 +2498,10 @@
       <c r="AW12" s="7"/>
     </row>
     <row r="13" spans="2:51" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="131" t="s">
+      <c r="C13" s="140" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="32" t="s">
@@ -2519,7 +2519,7 @@
       <c r="H13" s="64">
         <v>1</v>
       </c>
-      <c r="I13" s="137"/>
+      <c r="I13" s="101"/>
       <c r="J13" s="76"/>
       <c r="K13" s="78"/>
       <c r="L13" s="28"/>
@@ -2536,8 +2536,8 @@
       <c r="W13" s="33"/>
     </row>
     <row r="14" spans="2:51" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="121"/>
-      <c r="C14" s="133"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="142"/>
       <c r="D14" s="12" t="s">
         <v>35</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="H14" s="65">
         <v>2</v>
       </c>
-      <c r="I14" s="138"/>
+      <c r="I14" s="102"/>
       <c r="J14" s="79"/>
       <c r="K14" s="75"/>
       <c r="L14" s="19"/>
@@ -2570,10 +2570,10 @@
       <c r="W14" s="35"/>
     </row>
     <row r="15" spans="2:51" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="122" t="s">
+      <c r="B15" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="131" t="s">
+      <c r="C15" s="140" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="14" t="s">
@@ -2591,7 +2591,7 @@
       <c r="H15" s="64">
         <v>1</v>
       </c>
-      <c r="I15" s="138"/>
+      <c r="I15" s="102"/>
       <c r="J15" s="75"/>
       <c r="K15" s="27"/>
       <c r="L15" s="78"/>
@@ -2608,8 +2608,8 @@
       <c r="W15" s="33"/>
     </row>
     <row r="16" spans="2:51" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="123"/>
-      <c r="C16" s="132"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="141"/>
       <c r="D16" s="10" t="s">
         <v>127</v>
       </c>
@@ -2625,7 +2625,7 @@
       <c r="H16" s="66">
         <v>5</v>
       </c>
-      <c r="I16" s="138"/>
+      <c r="I16" s="102"/>
       <c r="J16" s="81"/>
       <c r="K16" s="79"/>
       <c r="L16" s="77"/>
@@ -2642,8 +2642,8 @@
       <c r="W16" s="34"/>
     </row>
     <row r="17" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="123"/>
-      <c r="C17" s="116" t="s">
+      <c r="B17" s="130"/>
+      <c r="C17" s="123" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="10" t="s">
@@ -2661,7 +2661,7 @@
       <c r="H17" s="66">
         <v>2</v>
       </c>
-      <c r="I17" s="138"/>
+      <c r="I17" s="102"/>
       <c r="J17" s="79"/>
       <c r="K17" s="76"/>
       <c r="L17" s="11"/>
@@ -2678,8 +2678,8 @@
       <c r="W17" s="34"/>
     </row>
     <row r="18" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="123"/>
-      <c r="C18" s="118"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="125"/>
       <c r="D18" s="10" t="s">
         <v>41</v>
       </c>
@@ -2695,7 +2695,7 @@
       <c r="H18" s="66">
         <v>2</v>
       </c>
-      <c r="I18" s="138"/>
+      <c r="I18" s="102"/>
       <c r="J18" s="79"/>
       <c r="K18" s="76"/>
       <c r="L18" s="11"/>
@@ -2712,7 +2712,7 @@
       <c r="W18" s="34"/>
     </row>
     <row r="19" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="124"/>
+      <c r="B19" s="131"/>
       <c r="C19" s="12" t="s">
         <v>42</v>
       </c>
@@ -2731,7 +2731,7 @@
       <c r="H19" s="65">
         <v>2</v>
       </c>
-      <c r="I19" s="138"/>
+      <c r="I19" s="102"/>
       <c r="J19" s="79"/>
       <c r="K19" s="75"/>
       <c r="L19" s="19"/>
@@ -2748,10 +2748,10 @@
       <c r="W19" s="35"/>
     </row>
     <row r="20" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="101" t="s">
+      <c r="B20" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="119" t="s">
+      <c r="C20" s="126" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="14" t="s">
@@ -2769,7 +2769,7 @@
       <c r="H20" s="64">
         <v>1</v>
       </c>
-      <c r="I20" s="138"/>
+      <c r="I20" s="102"/>
       <c r="J20" s="75"/>
       <c r="K20" s="27"/>
       <c r="L20" s="28"/>
@@ -2786,8 +2786,8 @@
       <c r="W20" s="33"/>
     </row>
     <row r="21" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="125"/>
-      <c r="C21" s="118"/>
+      <c r="B21" s="133"/>
+      <c r="C21" s="125"/>
       <c r="D21" s="10" t="s">
         <v>45</v>
       </c>
@@ -2803,7 +2803,7 @@
       <c r="H21" s="66">
         <v>1</v>
       </c>
-      <c r="I21" s="138"/>
+      <c r="I21" s="102"/>
       <c r="J21" s="80"/>
       <c r="K21" s="76"/>
       <c r="L21" s="11"/>
@@ -2820,7 +2820,7 @@
       <c r="W21" s="34"/>
     </row>
     <row r="22" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="103"/>
+      <c r="B22" s="134"/>
       <c r="C22" s="12" t="s">
         <v>46</v>
       </c>
@@ -2839,7 +2839,7 @@
       <c r="H22" s="65">
         <v>1</v>
       </c>
-      <c r="I22" s="138"/>
+      <c r="I22" s="102"/>
       <c r="J22" s="82"/>
       <c r="K22" s="76"/>
       <c r="L22" s="19"/>
@@ -2856,10 +2856,10 @@
       <c r="W22" s="35"/>
     </row>
     <row r="23" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="126" t="s">
+      <c r="B23" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="144" t="s">
         <v>48</v>
       </c>
       <c r="D23" s="14" t="s">
@@ -2877,7 +2877,7 @@
       <c r="H23" s="64">
         <v>1</v>
       </c>
-      <c r="I23" s="138"/>
+      <c r="I23" s="102"/>
       <c r="J23" s="83"/>
       <c r="K23" s="76"/>
       <c r="L23" s="28"/>
@@ -2894,8 +2894,8 @@
       <c r="W23" s="33"/>
     </row>
     <row r="24" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="127"/>
-      <c r="C24" s="105"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="145"/>
       <c r="D24" s="18" t="s">
         <v>93</v>
       </c>
@@ -2911,7 +2911,7 @@
       <c r="H24" s="67">
         <v>1</v>
       </c>
-      <c r="I24" s="138"/>
+      <c r="I24" s="102"/>
       <c r="J24" s="84"/>
       <c r="K24" s="75"/>
       <c r="L24" s="26"/>
@@ -2928,8 +2928,8 @@
       <c r="W24" s="36"/>
     </row>
     <row r="25" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="127"/>
-      <c r="C25" s="105"/>
+      <c r="B25" s="136"/>
+      <c r="C25" s="145"/>
       <c r="D25" s="18" t="s">
         <v>120</v>
       </c>
@@ -2945,7 +2945,7 @@
       <c r="H25" s="67">
         <v>2</v>
       </c>
-      <c r="I25" s="138"/>
+      <c r="I25" s="102"/>
       <c r="J25" s="47"/>
       <c r="K25" s="11"/>
       <c r="L25" s="27"/>
@@ -2962,8 +2962,8 @@
       <c r="W25" s="36"/>
     </row>
     <row r="26" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="127"/>
-      <c r="C26" s="106"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="146"/>
       <c r="D26" s="18" t="s">
         <v>94</v>
       </c>
@@ -2979,7 +2979,7 @@
       <c r="H26" s="67">
         <v>2</v>
       </c>
-      <c r="I26" s="138"/>
+      <c r="I26" s="102"/>
       <c r="J26" s="47"/>
       <c r="L26" s="75"/>
       <c r="M26" s="87"/>
@@ -2995,8 +2995,8 @@
       <c r="W26" s="36"/>
     </row>
     <row r="27" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="128"/>
-      <c r="C27" s="107" t="s">
+      <c r="B27" s="137"/>
+      <c r="C27" s="147" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="10" t="s">
@@ -3014,7 +3014,7 @@
       <c r="H27" s="66">
         <v>2</v>
       </c>
-      <c r="I27" s="138"/>
+      <c r="I27" s="102"/>
       <c r="J27" s="39"/>
       <c r="K27" s="11"/>
       <c r="L27" s="86"/>
@@ -3031,8 +3031,8 @@
       <c r="W27" s="34"/>
     </row>
     <row r="28" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="128"/>
-      <c r="C28" s="105"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="145"/>
       <c r="D28" s="10" t="s">
         <v>50</v>
       </c>
@@ -3048,7 +3048,7 @@
       <c r="H28" s="66">
         <v>2</v>
       </c>
-      <c r="I28" s="138"/>
+      <c r="I28" s="102"/>
       <c r="J28" s="39"/>
       <c r="K28" s="11"/>
       <c r="L28" s="86"/>
@@ -3065,8 +3065,8 @@
       <c r="W28" s="34"/>
     </row>
     <row r="29" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="128"/>
-      <c r="C29" s="106"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="146"/>
       <c r="D29" s="10" t="s">
         <v>95</v>
       </c>
@@ -3082,7 +3082,7 @@
       <c r="H29" s="66">
         <v>2</v>
       </c>
-      <c r="I29" s="138"/>
+      <c r="I29" s="102"/>
       <c r="J29" s="39"/>
       <c r="K29" s="53"/>
       <c r="L29" s="90"/>
@@ -3099,8 +3099,8 @@
       <c r="W29" s="34"/>
     </row>
     <row r="30" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="128"/>
-      <c r="C30" s="107" t="s">
+      <c r="B30" s="137"/>
+      <c r="C30" s="147" t="s">
         <v>51</v>
       </c>
       <c r="D30" s="10" t="s">
@@ -3118,7 +3118,7 @@
       <c r="H30" s="66">
         <v>3</v>
       </c>
-      <c r="I30" s="138"/>
+      <c r="I30" s="102"/>
       <c r="J30" s="80"/>
       <c r="K30" s="76"/>
       <c r="L30" s="85"/>
@@ -3135,8 +3135,8 @@
       <c r="W30" s="34"/>
     </row>
     <row r="31" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="128"/>
-      <c r="C31" s="105"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="145"/>
       <c r="D31" s="10" t="s">
         <v>99</v>
       </c>
@@ -3152,7 +3152,7 @@
       <c r="H31" s="66">
         <v>1</v>
       </c>
-      <c r="I31" s="138"/>
+      <c r="I31" s="102"/>
       <c r="J31" s="80"/>
       <c r="K31" s="75"/>
       <c r="L31" s="53"/>
@@ -3169,8 +3169,8 @@
       <c r="W31" s="34"/>
     </row>
     <row r="32" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="128"/>
-      <c r="C32" s="105"/>
+      <c r="B32" s="137"/>
+      <c r="C32" s="145"/>
       <c r="D32" s="10" t="s">
         <v>100</v>
       </c>
@@ -3186,7 +3186,7 @@
       <c r="H32" s="66">
         <v>2</v>
       </c>
-      <c r="I32" s="138"/>
+      <c r="I32" s="102"/>
       <c r="J32" s="39"/>
       <c r="K32" s="86"/>
       <c r="L32" s="77"/>
@@ -3203,8 +3203,8 @@
       <c r="W32" s="34"/>
     </row>
     <row r="33" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="128"/>
-      <c r="C33" s="105"/>
+      <c r="B33" s="137"/>
+      <c r="C33" s="145"/>
       <c r="D33" s="10" t="s">
         <v>114</v>
       </c>
@@ -3220,7 +3220,7 @@
       <c r="H33" s="66">
         <v>2</v>
       </c>
-      <c r="I33" s="138"/>
+      <c r="I33" s="102"/>
       <c r="J33" s="39"/>
       <c r="K33" s="11"/>
       <c r="L33" s="90"/>
@@ -3237,8 +3237,8 @@
       <c r="W33" s="34"/>
     </row>
     <row r="34" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="128"/>
-      <c r="C34" s="106"/>
+      <c r="B34" s="137"/>
+      <c r="C34" s="146"/>
       <c r="D34" s="10" t="s">
         <v>98</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="H34" s="66">
         <v>2</v>
       </c>
-      <c r="I34" s="138"/>
+      <c r="I34" s="102"/>
       <c r="J34" s="39"/>
       <c r="K34" s="90"/>
       <c r="L34" s="76"/>
@@ -3271,8 +3271,8 @@
       <c r="W34" s="34"/>
     </row>
     <row r="35" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="128"/>
-      <c r="C35" s="107" t="s">
+      <c r="B35" s="137"/>
+      <c r="C35" s="147" t="s">
         <v>52</v>
       </c>
       <c r="D35" s="10" t="s">
@@ -3290,7 +3290,7 @@
       <c r="H35" s="66">
         <v>3</v>
       </c>
-      <c r="I35" s="138"/>
+      <c r="I35" s="102"/>
       <c r="J35" s="80"/>
       <c r="K35" s="77"/>
       <c r="L35" s="79"/>
@@ -3307,8 +3307,8 @@
       <c r="W35" s="34"/>
     </row>
     <row r="36" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="129"/>
-      <c r="C36" s="105"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="145"/>
       <c r="D36" s="49" t="s">
         <v>102</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="H36" s="68">
         <v>2</v>
       </c>
-      <c r="I36" s="138"/>
+      <c r="I36" s="102"/>
       <c r="J36" s="51"/>
       <c r="K36" s="90"/>
       <c r="L36" s="76"/>
@@ -3341,8 +3341,8 @@
       <c r="W36" s="54"/>
     </row>
     <row r="37" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="129"/>
-      <c r="C37" s="105"/>
+      <c r="B37" s="138"/>
+      <c r="C37" s="145"/>
       <c r="D37" s="49" t="s">
         <v>103</v>
       </c>
@@ -3358,7 +3358,7 @@
       <c r="H37" s="68">
         <v>2</v>
       </c>
-      <c r="I37" s="138"/>
+      <c r="I37" s="102"/>
       <c r="J37" s="51"/>
       <c r="K37" s="90"/>
       <c r="L37" s="75"/>
@@ -3375,8 +3375,8 @@
       <c r="W37" s="54"/>
     </row>
     <row r="38" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="129"/>
-      <c r="C38" s="105"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="145"/>
       <c r="D38" s="49" t="s">
         <v>122</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="H38" s="68">
         <v>2</v>
       </c>
-      <c r="I38" s="138"/>
+      <c r="I38" s="102"/>
       <c r="J38" s="51"/>
       <c r="K38" s="53"/>
       <c r="L38" s="93"/>
@@ -3409,8 +3409,8 @@
       <c r="W38" s="54"/>
     </row>
     <row r="39" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="129"/>
-      <c r="C39" s="106"/>
+      <c r="B39" s="138"/>
+      <c r="C39" s="146"/>
       <c r="D39" s="49" t="s">
         <v>104</v>
       </c>
@@ -3426,7 +3426,7 @@
       <c r="H39" s="68">
         <v>3</v>
       </c>
-      <c r="I39" s="138"/>
+      <c r="I39" s="102"/>
       <c r="J39" s="51"/>
       <c r="K39" s="90"/>
       <c r="L39" s="75"/>
@@ -3443,8 +3443,8 @@
       <c r="W39" s="54"/>
     </row>
     <row r="40" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="129"/>
-      <c r="C40" s="107" t="s">
+      <c r="B40" s="138"/>
+      <c r="C40" s="147" t="s">
         <v>53</v>
       </c>
       <c r="D40" s="49" t="s">
@@ -3462,7 +3462,7 @@
       <c r="H40" s="68">
         <v>2</v>
       </c>
-      <c r="I40" s="138"/>
+      <c r="I40" s="102"/>
       <c r="J40" s="81"/>
       <c r="K40" s="75"/>
       <c r="L40" s="75"/>
@@ -3479,8 +3479,8 @@
       <c r="W40" s="54"/>
     </row>
     <row r="41" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="129"/>
-      <c r="C41" s="105"/>
+      <c r="B41" s="138"/>
+      <c r="C41" s="145"/>
       <c r="D41" s="49" t="s">
         <v>115</v>
       </c>
@@ -3496,7 +3496,7 @@
       <c r="H41" s="68">
         <v>2</v>
       </c>
-      <c r="I41" s="138"/>
+      <c r="I41" s="102"/>
       <c r="J41" s="81"/>
       <c r="K41" s="75"/>
       <c r="L41" s="75"/>
@@ -3513,8 +3513,8 @@
       <c r="W41" s="54"/>
     </row>
     <row r="42" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="129"/>
-      <c r="C42" s="105"/>
+      <c r="B42" s="138"/>
+      <c r="C42" s="145"/>
       <c r="D42" s="49" t="s">
         <v>116</v>
       </c>
@@ -3530,7 +3530,7 @@
       <c r="H42" s="68">
         <v>3</v>
       </c>
-      <c r="I42" s="138"/>
+      <c r="I42" s="102"/>
       <c r="J42" s="51"/>
       <c r="K42" s="93"/>
       <c r="L42" s="75"/>
@@ -3547,8 +3547,8 @@
       <c r="W42" s="54"/>
     </row>
     <row r="43" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="130"/>
-      <c r="C43" s="108"/>
+      <c r="B43" s="139"/>
+      <c r="C43" s="148"/>
       <c r="D43" s="12" t="s">
         <v>133</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="H43" s="65">
         <v>2</v>
       </c>
-      <c r="I43" s="138"/>
+      <c r="I43" s="102"/>
       <c r="J43" s="38"/>
       <c r="K43" s="19"/>
       <c r="L43" s="94"/>
@@ -3581,7 +3581,7 @@
       <c r="W43" s="35"/>
     </row>
     <row r="44" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="126" t="s">
+      <c r="B44" s="135" t="s">
         <v>54</v>
       </c>
       <c r="C44" s="57" t="s">
@@ -3602,7 +3602,7 @@
       <c r="H44" s="64">
         <v>2</v>
       </c>
-      <c r="I44" s="138"/>
+      <c r="I44" s="102"/>
       <c r="J44" s="37"/>
       <c r="K44" s="28"/>
       <c r="L44" s="28"/>
@@ -3619,7 +3619,7 @@
       <c r="W44" s="33"/>
     </row>
     <row r="45" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="128"/>
+      <c r="B45" s="137"/>
       <c r="C45" s="58" t="s">
         <v>58</v>
       </c>
@@ -3638,7 +3638,7 @@
       <c r="H45" s="66">
         <v>2</v>
       </c>
-      <c r="I45" s="138"/>
+      <c r="I45" s="102"/>
       <c r="J45" s="39"/>
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
@@ -3655,7 +3655,7 @@
       <c r="W45" s="34"/>
     </row>
     <row r="46" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="128"/>
+      <c r="B46" s="137"/>
       <c r="C46" s="58" t="s">
         <v>110</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="H46" s="66">
         <v>2</v>
       </c>
-      <c r="I46" s="138"/>
+      <c r="I46" s="102"/>
       <c r="J46" s="39"/>
       <c r="K46" s="11"/>
       <c r="L46" s="75"/>
@@ -3691,7 +3691,7 @@
       <c r="W46" s="34"/>
     </row>
     <row r="47" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="128"/>
+      <c r="B47" s="137"/>
       <c r="C47" s="58" t="s">
         <v>111</v>
       </c>
@@ -3710,7 +3710,7 @@
       <c r="H47" s="66">
         <v>2</v>
       </c>
-      <c r="I47" s="138"/>
+      <c r="I47" s="102"/>
       <c r="J47" s="39"/>
       <c r="K47" s="11"/>
       <c r="L47" s="75"/>
@@ -3727,8 +3727,8 @@
       <c r="W47" s="34"/>
     </row>
     <row r="48" spans="2:23" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="128"/>
-      <c r="C48" s="116" t="s">
+      <c r="B48" s="137"/>
+      <c r="C48" s="123" t="s">
         <v>123</v>
       </c>
       <c r="D48" s="10" t="s">
@@ -3746,7 +3746,7 @@
       <c r="H48" s="66">
         <v>1</v>
       </c>
-      <c r="I48" s="138"/>
+      <c r="I48" s="102"/>
       <c r="J48" s="39"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
@@ -3763,8 +3763,8 @@
       <c r="W48" s="34"/>
     </row>
     <row r="49" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="128"/>
-      <c r="C49" s="117"/>
+      <c r="B49" s="137"/>
+      <c r="C49" s="124"/>
       <c r="D49" s="10" t="s">
         <v>125</v>
       </c>
@@ -3780,7 +3780,7 @@
       <c r="H49" s="66">
         <v>2</v>
       </c>
-      <c r="I49" s="138"/>
+      <c r="I49" s="102"/>
       <c r="J49" s="39"/>
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
@@ -3797,8 +3797,8 @@
       <c r="W49" s="34"/>
     </row>
     <row r="50" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="128"/>
-      <c r="C50" s="118"/>
+      <c r="B50" s="137"/>
+      <c r="C50" s="125"/>
       <c r="D50" s="10" t="s">
         <v>126</v>
       </c>
@@ -3814,7 +3814,7 @@
       <c r="H50" s="66">
         <v>1</v>
       </c>
-      <c r="I50" s="138"/>
+      <c r="I50" s="102"/>
       <c r="J50" s="39"/>
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
@@ -3831,7 +3831,7 @@
       <c r="W50" s="34"/>
     </row>
     <row r="51" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="128"/>
+      <c r="B51" s="137"/>
       <c r="C51" s="73" t="s">
         <v>129</v>
       </c>
@@ -3850,7 +3850,7 @@
       <c r="H51" s="66">
         <v>1</v>
       </c>
-      <c r="I51" s="138"/>
+      <c r="I51" s="102"/>
       <c r="J51" s="39"/>
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
@@ -3867,7 +3867,7 @@
       <c r="W51" s="34"/>
     </row>
     <row r="52" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="128"/>
+      <c r="B52" s="137"/>
       <c r="C52" s="58" t="s">
         <v>117</v>
       </c>
@@ -3886,7 +3886,7 @@
       <c r="H52" s="66">
         <v>2</v>
       </c>
-      <c r="I52" s="138"/>
+      <c r="I52" s="102"/>
       <c r="J52" s="39"/>
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
@@ -3903,8 +3903,8 @@
       <c r="W52" s="34"/>
     </row>
     <row r="53" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="128"/>
-      <c r="C53" s="116" t="s">
+      <c r="B53" s="137"/>
+      <c r="C53" s="123" t="s">
         <v>60</v>
       </c>
       <c r="D53" s="10" t="s">
@@ -3922,7 +3922,7 @@
       <c r="H53" s="66">
         <v>5</v>
       </c>
-      <c r="I53" s="138"/>
+      <c r="I53" s="102"/>
       <c r="J53" s="39"/>
       <c r="K53" s="11"/>
       <c r="L53" s="75"/>
@@ -3942,8 +3942,8 @@
       </c>
     </row>
     <row r="54" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="128"/>
-      <c r="C54" s="117"/>
+      <c r="B54" s="137"/>
+      <c r="C54" s="124"/>
       <c r="D54" s="63" t="s">
         <v>119</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="H54" s="66">
         <v>2</v>
       </c>
-      <c r="I54" s="138"/>
+      <c r="I54" s="102"/>
       <c r="J54" s="39"/>
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
@@ -3976,8 +3976,8 @@
       <c r="W54" s="34"/>
     </row>
     <row r="55" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="128"/>
-      <c r="C55" s="118"/>
+      <c r="B55" s="137"/>
+      <c r="C55" s="125"/>
       <c r="D55" s="10" t="s">
         <v>121</v>
       </c>
@@ -3993,7 +3993,7 @@
       <c r="H55" s="66">
         <v>2</v>
       </c>
-      <c r="I55" s="138"/>
+      <c r="I55" s="102"/>
       <c r="J55" s="39"/>
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>
@@ -4010,7 +4010,7 @@
       <c r="W55" s="34"/>
     </row>
     <row r="56" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="128"/>
+      <c r="B56" s="137"/>
       <c r="C56" s="58" t="s">
         <v>62</v>
       </c>
@@ -4029,7 +4029,7 @@
       <c r="H56" s="66">
         <v>3</v>
       </c>
-      <c r="I56" s="138"/>
+      <c r="I56" s="102"/>
       <c r="J56" s="39"/>
       <c r="K56" s="11"/>
       <c r="L56" s="11"/>
@@ -4046,7 +4046,7 @@
       <c r="W56" s="34"/>
     </row>
     <row r="57" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="129"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="74" t="s">
         <v>64</v>
       </c>
@@ -4065,7 +4065,7 @@
       <c r="H57" s="68">
         <v>2</v>
       </c>
-      <c r="I57" s="138"/>
+      <c r="I57" s="102"/>
       <c r="J57" s="38"/>
       <c r="K57" s="19"/>
       <c r="L57" s="19"/>
@@ -4082,7 +4082,7 @@
       <c r="W57" s="35"/>
     </row>
     <row r="58" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="101" t="s">
+      <c r="B58" s="132" t="s">
         <v>67</v>
       </c>
       <c r="C58" s="14" t="s">
@@ -4103,7 +4103,7 @@
       <c r="H58" s="64">
         <v>3</v>
       </c>
-      <c r="I58" s="138"/>
+      <c r="I58" s="102"/>
       <c r="J58" s="37"/>
       <c r="K58" s="28"/>
       <c r="L58" s="28"/>
@@ -4120,7 +4120,7 @@
       <c r="W58" s="33"/>
     </row>
     <row r="59" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="102"/>
+      <c r="B59" s="143"/>
       <c r="C59" s="10" t="s">
         <v>68</v>
       </c>
@@ -4139,7 +4139,7 @@
       <c r="H59" s="66">
         <v>3</v>
       </c>
-      <c r="I59" s="138"/>
+      <c r="I59" s="102"/>
       <c r="J59" s="39"/>
       <c r="K59" s="11"/>
       <c r="L59" s="11"/>
@@ -4156,7 +4156,7 @@
       <c r="W59" s="34"/>
     </row>
     <row r="60" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="102"/>
+      <c r="B60" s="143"/>
       <c r="C60" s="10" t="s">
         <v>136</v>
       </c>
@@ -4175,7 +4175,7 @@
       <c r="H60" s="66">
         <v>3</v>
       </c>
-      <c r="I60" s="138"/>
+      <c r="I60" s="102"/>
       <c r="J60" s="39"/>
       <c r="K60" s="11"/>
       <c r="L60" s="11"/>
@@ -4192,7 +4192,7 @@
       <c r="W60" s="34"/>
     </row>
     <row r="61" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="102"/>
+      <c r="B61" s="143"/>
       <c r="C61" s="10" t="s">
         <v>137</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="H61" s="66">
         <v>3</v>
       </c>
-      <c r="I61" s="138"/>
+      <c r="I61" s="102"/>
       <c r="J61" s="39"/>
       <c r="K61" s="11"/>
       <c r="L61" s="11"/>
@@ -4228,8 +4228,8 @@
       <c r="W61" s="34"/>
     </row>
     <row r="62" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="102"/>
-      <c r="C62" s="107" t="s">
+      <c r="B62" s="143"/>
+      <c r="C62" s="147" t="s">
         <v>69</v>
       </c>
       <c r="D62" s="55" t="s">
@@ -4247,7 +4247,7 @@
       <c r="H62" s="69">
         <v>3</v>
       </c>
-      <c r="I62" s="138"/>
+      <c r="I62" s="102"/>
       <c r="J62" s="39"/>
       <c r="K62" s="11"/>
       <c r="L62" s="11"/>
@@ -4264,8 +4264,8 @@
       <c r="W62" s="34"/>
     </row>
     <row r="63" spans="2:29" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="103"/>
-      <c r="C63" s="108"/>
+      <c r="B63" s="134"/>
+      <c r="C63" s="148"/>
       <c r="D63" s="12" t="s">
         <v>107</v>
       </c>
@@ -4281,7 +4281,7 @@
       <c r="H63" s="65">
         <v>2</v>
       </c>
-      <c r="I63" s="138"/>
+      <c r="I63" s="102"/>
       <c r="J63" s="38"/>
       <c r="K63" s="19"/>
       <c r="L63" s="19"/>
@@ -4319,7 +4319,7 @@
       <c r="H64" s="70">
         <v>2</v>
       </c>
-      <c r="I64" s="139"/>
+      <c r="I64" s="103"/>
       <c r="J64" s="41"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
@@ -4338,20 +4338,13 @@
   </sheetData>
   <autoFilter ref="G10:G64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="35">
-    <mergeCell ref="I13:I64"/>
-    <mergeCell ref="J11:O11"/>
-    <mergeCell ref="P11:V11"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="J10:W10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C30:C34"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="C40:C43"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
@@ -4366,13 +4359,20 @@
     <mergeCell ref="C48:C50"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C30:C34"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="I13:I64"/>
+    <mergeCell ref="J11:O11"/>
+    <mergeCell ref="P11:V11"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="J10:W10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
